--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1009.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1009.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>作成: 2026-09-29 荒木田（ドラフト）。rev2 2026-09-30: 校閲版（0930_rev1_g）の赤字を反映（MC 文言の修正、RT 案内の箇条書き化、Co-Chair への確認依頼）。10/8（木）全体ブリーフィング（SCDF emcee・モデレーター、Google Meet）用。 rev3 2026-10-04: Opening の登壇順をアジェンダ順（Commissioner→林室長→三浦センター長が開会宣言）に確定（Sylvia 10/2 WhatsApp 確認）。PPT 03〜06 の割当、三浦原稿（draft1002_clean）の参照を更新。 同日: Azerbaijan の RT 発言辞退（10/1）を反映して Day1 の行を削除、以降の時刻と PPT 09 番号を繰り上げ。 10/5: 三浦センター長が開会・閉会挨拶案を了承（確定）。 10/6: Lao PDR の RT 発言辞退（10/5 吉田）で Day1 の行を削除、Pakistan 登録。 1006b: 林氏の日本語肩書を「林室長」に統一（英語は Deputy Minister for Disaster Management のまま）。 1006c: TS 発表 2 の JAXA を松尾氏に（池田 10/5）。 1008: 10/8 SCDF MC ブリーフィングの結果を反映（Joint Opening 後の動線、Opening 後の集合写真〈ステージ上、RT を 5 分繰下げ〉、SCDF 閉会挨拶を削除し MC の一言に、Commissioner は Opening のみ、RT コメント方式、タイムキーパー、シンガポール発言者、フィールドトリップ・パレードの時刻）。 rev4 2026-10-09: TS の順番と時間配分を池田さん 10/7 時間割（荒木田修正版コンセプトノート 1007）に合わせた（ウズベキスタン 1 番目 10 分、Google・BRIN・YI-Lab・JAXA 各 15 分、日本 3 件各 10 分、質疑 10 分、まとめ 5 分）。ポケトーク再開時刻を 10:15 に。</t>
+          <t>作成: 2026-09-29 荒木田（ドラフト）。rev2 2026-09-30: 校閲版（0930_rev1_g）の赤字を反映（MC 文言の修正、RT 案内の箇条書き化、Co-Chair への確認依頼）。10/8（木）全体ブリーフィング（SCDF emcee・モデレーター、Google Meet）用。 rev3 2026-10-04: Opening の登壇順をアジェンダ順（Commissioner→林室長→三浦センター長が開会宣言）に確定（Sylvia 10/2 WhatsApp 確認）。PPT 03〜06 の割当、三浦原稿（draft1002_clean）の参照を更新。 同日: Azerbaijan の RT 発言辞退（10/1）を反映して Day1 の行を削除、以降の時刻と PPT 09 番号を繰り上げ。 10/5: 三浦センター長が開会・閉会挨拶案を了承（確定）。 10/6: Lao PDR の RT 発言辞退（10/5 吉田）で Day1 の行を削除、Pakistan 登録。 1006b: 林氏の日本語肩書を「林室長」に統一（英語は Deputy Minister for Disaster Management のまま）。 1006c: TS 発表 2 の JAXA を松尾氏に（池田 10/5）。 1008: 10/8 SCDF MC ブリーフィングの結果を反映（Joint Opening 後の動線、Opening 後の集合写真〈ステージ上、RT を 5 分繰下げ〉、SCDF 閉会挨拶を削除し MC の一言に、Commissioner は Opening のみ、RT コメント方式、タイムキーパー、シンガポール発言者、フィールドトリップ・パレードの時刻）。 rev4 2026-10-09: TS の順番と時間配分を池田さん 10/7 時間割（荒木田修正版コンセプトノート 1007）に合わせた（ウズベキスタン 1 番目 10 分、Google・BRIN・YI-Lab・JAXA 各 15 分、日本 3 件各 10 分、質疑 10 分、まとめ 5 分）。ポケトーク再開時刻を 10:15 に。 同日: ポケトークの QR は進行スライドと参加者の WhatsApp で共有し、卓上カードはやめた（荒木田）。</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>・会場: Peridot 204-206, Singapore EXPO。使用言語: 英語。Zoom Webinar による双方向ハイブリッド（オンライン登壇の可能性: UNDP・WMO＝未登録）。AI通訳（日本語）は神戸側が監視。
-・AI 翻訳＝ポケトークライブ（Sentio）。ホストは神戸（中村）が Zoom の音声を入力して運用する。参加者は QR（PPT 08 と卓上カード）を読み、自分の携帯や PC で翻訳言語を選んで読む。会場スクリーンへの字幕投影はしない。QR/URL は神戸が共有を開始した時点で発行されるので事前印刷はできない（共有開始直後に神戸が QR 画像を現地へ送り、現地でスライド貼付と案内カード印刷）。仕様（プレミアムプラン、pocketalk.jp/sentio/lineup・取扱説明書 10/1 確認）: 通訳の連続利用は 1 回 90 分、月の累計は無制限、共有可能人数 50 名、共有 URL/QR は共有開始から 6 時間で自動破棄。カンファレンスプランは連続無制限・URL 固定・50 名超も可（見積り制、リハーサル無償）。→ 運用: 通訳は 90 分ごとに藤本が再開（28 日 14:08 頃＝RT 13 番目の発言者の後、29 日 10:20 頃＝TS 発表 3 と 4 の間、11:40 頃＝閉会前）。共有 URL は本番用を 28 日 12:40、29 日 08:55 に開始する（08:00 の接続テストで開いた共有は必ず終了。6 時間で URL が破棄されるため、テストの共有をそのまま使うと 14:00 頃に切れる）。通訳を再開しても同じ共有 URL が維持されるかは神戸のリハーサルで検証（維持されるなら QR の再掲示は不要。されない場合は再開時に新 QR＝PPT 08b／16b を 20 秒表示し MC が再読込みを案内）。同時閲覧 50 名を超える見込み（日本語字幕の需要が多い場合）ならカンファレンスプランの見積りを取る。担当: 現地一次対応 藤本、設定 中村（神戸）。</t>
+・AI 翻訳＝ポケトークライブ（Sentio）。ホストは神戸（中村）が Zoom の音声を入力して運用する。参加者は QR（PPT 08 と WhatsApp で共有）を読み、自分の携帯や PC で翻訳言語を選んで読む。会場スクリーンへの字幕投影はしない。QR/URL は神戸が共有を開始した時点で発行されるので事前印刷はできない（共有開始直後に神戸が QR 画像を現地へ送り、現地でスライドに貼り、参加者の WhatsApp に共有）。仕様（プレミアムプラン、pocketalk.jp/sentio/lineup・取扱説明書 10/1 確認）: 通訳の連続利用は 1 回 90 分、月の累計は無制限、共有可能人数 50 名、共有 URL/QR は共有開始から 6 時間で自動破棄。カンファレンスプランは連続無制限・URL 固定・50 名超も可（見積り制、リハーサル無償）。→ 運用: 通訳は 90 分ごとに藤本が再開（28 日 14:08 頃＝RT 13 番目の発言者の後、29 日 10:20 頃＝TS 発表 3 と 4 の間、11:40 頃＝閉会前）。共有 URL は本番用を 28 日 12:40、29 日 08:55 に開始する（08:00 の接続テストで開いた共有は必ず終了。6 時間で URL が破棄されるため、テストの共有をそのまま使うと 14:00 頃に切れる）。通訳を再開しても同じ共有 URL が維持されるかは神戸のリハーサルで検証（維持されるなら QR の再掲示は不要。されない場合は再開時に新 QR＝PPT 08b／16b を 20 秒表示し MC が再読込みを案内）。同時閲覧 50 名を超える見込み（日本語字幕の需要が多い場合）ならカンファレンスプランの見積りを取る。担当: 現地一次対応 藤本、設定 中村（神戸）。</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林室長、三浦センター長）は12:40までに着席。12:40 神戸（中村）が Sentio の共有を開始し通訳を開始（共有 URL は 6 時間有効、通訳は 90 分で再開が必要 → 14:08 頃に神戸が再開）。QR は共有開始後にしか発行されないため事前印刷は不可。共有開始直後に神戸から WhatsApp で届く QR 画像を藤本が PPT 08 に貼り、田中がポータブルプリンターで卓上の案内カードを印刷して 12:45 までに配る（間に合わなければ PPT 08 の掲示のみ）。参加者は各自の携帯や PC で言語を選ぶ。</t>
+          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林室長、三浦センター長）は12:40までに着席。12:40 神戸（中村）が Sentio の共有を開始し通訳を開始（共有 URL は 6 時間有効、通訳は 90 分で再開が必要 → 14:08 頃に神戸が再開）。QR は共有開始後にしか発行されないため事前印刷は不可。共有開始直後に神戸から WhatsApp で届く QR 画像を藤本が PPT 08 に貼り、参加者の WhatsApp にも共有する（卓上カードは作らない、10/9 荒木田）。参加者は各自の携帯や PC で言語を選ぶ。</t>
         </is>
       </c>
       <c r="G8" s="6" t="n"/>
@@ -4077,7 +4077,7 @@
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>【ポケトークライブ】通訳は 08:55 開始分が 10:25 で 90 分に達するため、発表 3 件目（BRIN 10:00-10:15）の後に神戸（中村）が通訳を再開（藤本が WhatsApp で合図）。共有 URL が維持されない場合のみ新 QR スライド（PPT 16b）を 20 秒表示し Moderator が再読込みを案内。29 日の QR も 08:55 に神戸が共有を開始した後に届くため、PPT 08 への貼付と案内カードの印刷は 08:55〜09:00 に行う（RT Part 2 開始時は PPT 掲示のみでも可）。Moderator: LTC Chen Yong Kai（SCDF）。Co-Chair: Dr. Mizan Bisri（ADRC）。PIC・タイムキーパー: 池田。AV/Zoom: 荒木田。カメラ・フロア: 塩見。配分（池田 10/7 時間割、荒木田修正版コンセプトノート 1007）: 紹介5分＋ウズベキスタン10分＋海外・JAXA 15分×4＋日本 10分×3＋質疑10分＋まとめ5分。10/9 11:00 の TS ブリーフィングで確定。</t>
+          <t>【ポケトークライブ】通訳は 08:55 開始分が 10:25 で 90 分に達するため、発表 3 件目（BRIN 10:00-10:15）の後に神戸（中村）が通訳を再開（藤本が WhatsApp で合図）。共有 URL が維持されない場合のみ新 QR スライド（PPT 16b）を 20 秒表示し Moderator が再読込みを案内。29 日の QR も 08:55 に神戸が共有を開始した後に届くため、PPT 08 への貼付と参加者の WhatsApp への共有は 08:55〜09:00 に行う。Moderator: LTC Chen Yong Kai（SCDF）。Co-Chair: Dr. Mizan Bisri（ADRC）。PIC・タイムキーパー: 池田。AV/Zoom: 荒木田。カメラ・フロア: 塩見。配分（池田 10/7 時間割、荒木田修正版コンセプトノート 1007）: 紹介5分＋ウズベキスタン10分＋海外・JAXA 15分×4＋日本 10分×3＋質疑10分＋まとめ5分。10/9 11:00 の TS ブリーフィングで確定。</t>
         </is>
       </c>
       <c r="G17" s="6" t="n"/>

--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1009.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1009.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B15"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="2" max="2"/>
@@ -529,7 +529,7 @@
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>・時間配分: 開会挨拶は Commissioner 5分・林 4〜5分・三浦 約4分（最後に開会宣言）・MC 計1〜2分（15分枠）。三浦原稿は draft1002_clean（児玉 rev4 受入、551語＝約4分）。
+          <t>・時間配分: 開会挨拶は Commissioner 5分・林 約3分（原案3分以内・英文約400語、10/9）・三浦 約4分（最後に開会宣言）・MC 計1〜2分（15分枠）。三浦原稿は draft1002_clean（児玉 rev4 受入、551語＝約4分）。
 ・ADRC Opening 登壇順＝Commissioner → 林室長 → 三浦センター長（開会宣言）。アジェンダどおりの順で Sylvia 10/2 08:01 WhatsApp「We are ok with the order!」により確定（9/30 の暫定順〈三浦→Commissioner→林〉は取り下げ）。RT はメンバー国 各5分まで（荒木田 9/29 決定、ベル方式）、アドバイザー国・ADPC・その他機関は4分（荒木田 10/1 決定。吉田は機関 5分を提案、登録者数次第で再調整）。TS は rev1.0（紹介5分＋発表15分×6枠＋質疑15分＋まとめ10分）。</t>
         </is>
       </c>
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P40"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -988,7 +988,7 @@
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>所要15分＋集合写真5分。挨拶 Commissioner 5分・林室長 4〜5分・三浦センター長 約4分（最後に開会宣言）＋MC 約1分。登壇順はアジェンダどおりで Sylvia 10/2 08:01 WhatsApp 確認済み。Commissioner は Opening のみ出席し退席（10/8 Sylvia）。Opening 後にステージ上（スクリーン前）で集合写真（10/8 決定、3〜5分）。</t>
+          <t>所要15分＋集合写真5分。挨拶 Commissioner 5分・林室長 約3分・三浦センター長 約4分（最後に開会宣言）＋MC 約1分。登壇順はアジェンダどおりで Sylvia 10/2 08:01 WhatsApp 確認済み。Commissioner は Opening のみ出席し退席（10/8 Sylvia）。Opening 後にステージ上（スクリーン前）で集合写真（10/8 決定、3〜5分）。</t>
         </is>
       </c>
       <c r="G10" s="6" t="n"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>日本語AI通訳は Zoom 内のみ（会場では案内しない）。RT のコメント方式は 9/30 吉田さん回答で決定（時間があれば会場、なければ用紙かオンライン）。登壇順はアジェンダどおり Commissioner→林室長→三浦センター長（開会宣言）。Sylvia 10/2 08:01 WhatsApp「We are ok with the order!」で確定。持ち時間: Commissioner 5分・林 4〜5分・三浦 約4分・MC 計1〜2分。</t>
+          <t>日本語AI通訳は Zoom 内のみ（会場では案内しない）。RT のコメント方式は 9/30 吉田さん回答で決定（時間があれば会場、なければ用紙かオンライン）。登壇順はアジェンダどおり Commissioner→林室長→三浦センター長（開会宣言）。Sylvia 10/2 08:01 WhatsApp「We are ok with the order!」で確定。持ち時間: Commissioner 5分・林 約3分（原案3分以内・英文約400語、10/9）・三浦 約4分・MC 計1〜2分。</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1163,7 +1163,7 @@
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Next, I am pleased to invite Mr HAYASHI Masamichi, Deputy Minister for Disaster Management, Cabinet Office of Japan (COJ), to deliver his opening remarks. Deputy Minister Hayashi, please.
-（挨拶 4〜5分）
+（挨拶 約3分）
 Thank you very much, Deputy Minister Hayashi.</t>
         </is>
       </c>
@@ -3107,7 +3107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P33"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5099,7 +5099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:F25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>

--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1009.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1009.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="B1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="2" max="2"/>
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="B1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3107,7 +3107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="B1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4563,7 +4563,8 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>池田 10/7: 内閣府・WOTA・Spectee を仮に各 10 分（10:45-11:15）。WOTA・Spectee の氏名は入手次第（児玉 9/30: Spectee 根来氏・WOTA 郷坪氏の見込み、未確定）。前方席の入替なし。PPT 17-7・17-8 を追加する（スライド作成時）。</t>
+          <t>池田 10/7: 内閣府・WOTA・Spectee を仮に各 10 分（10:45-11:15）。WOTA・Spectee の氏名は入手次第（児玉 9/30: Spectee 根来氏・WOTA 郷坪氏の見込み、未確定）。前方席の入替なし。PPT 17-7・17-8 を追加する（スライド作成時）。
+席: 前方右卓は6席（Uzbekistan・Google・BRIN・YI-Lab・JAXA・内閣府）。WOTA・Spectee の2名はステージ上、日本（中根氏）の後ろに椅子のみ置き、発表時に演台へ（荒木田 10/9）。</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -5099,7 +5100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="B1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
